--- a/docs/spire_tools_modules.xlsx
+++ b/docs/spire_tools_modules.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dump\spire\01_QA_results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\home\bhagavan\pocs\spire\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839085D7-00C8-4430-A5A7-D2783F32575E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D54731-9227-4817-82B5-5C55769FAC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
